--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_002/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_002/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -409,11 +414,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -480,11 +480,6 @@
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1291,12 +1286,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Quasi-static and random vibration stress/strain analysis of 7075-T73 avionics tray bracket for Lot 2 machining release</t>
+          <t>Quasi-static and random vibration stress/strain prediction for 7075-T73 avionics tray bracket fillet</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023HF3 finite element analysis of machined 7075-T73 bracket (P/N LND-AV-312) under 1.8g axial / 1.2g lateral quasi-static ascent loads and random vibration (0.1 g^2/Hz @ 80–350 Hz, 10.1 g RMS OA). The model must bound stresses and strains at the critical fillet near the forward tie-down to support a no-design-change release decision for Lot 2 machining.</t>
+          <t>Abaqus/Standard 2023HF3 finite-element analysis of machined 7075-T73 bracket (P/N LND-AV-312) under 1.8g axial / 1.2g lateral quasi-static ascent loads and random vibration (0.1 g²/Hz, 80–350 Hz, 10.1 g RMS OA). Model is used to establish positive margin at the critical fillet near the forward tie-down and to support Lot 2 machining release decision (PR-1012).</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1334,9 +1329,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Structural adequacy requirement for Lot 2 release</t>
+          <t>Positive Margin at Critical Fillet — Lot 2 Release</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1465,7 +1460,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>The bracket must carry quasi-static ascent loads and random vibe with positive margin (≥50 MPa headroom to yield at 95th percentile) at the critical fillet features flagged in PR-1012, with peak plastic strain non-propagating (&lt;0.2%), sufficient to authorize Lot 2 machining without design change.</t>
+          <t>Bracket must carry quasi-static ascent loads (1.8g axial, 1.2g lateral) and random vibe (10.1 g RMS OA) with positive margin at the forward tie-down fillet, bounding stresses/strains at features flagged in PR-1012, to support Lot 2 machining release with no design change.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1487,12 +1482,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023HF3 FEA model of LND-AV-312 bracket</t>
+          <t>Abaqus/Standard 2023HF3 FEA Model — LND-AV-312</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Implicit FEA model using C3D10 solid tetra elements, beam bolt shanks, surface-to-surface penalty contact, bilinear kinematic plasticity for 7075-T73, with quasi-static and PSD vibe load steps.</t>
+          <t>Implicit small-strain elastic-plastic solid (C3D10) model of the avionics tray bracket with bolt-beam elements, surface contact, bilinear kinematic plasticity (7075-T73), and base-acceleration PSD loading.</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1499,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>MMPDS-17 7075-T73 material data and ultrasonic NDI stock cert correlation</t>
+          <t>MMPDS-17 Material Properties — 7075-T73</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Material properties (E = 71.5 GPa, ν = 0.33, yield = 365 MPa) sourced from MMPDS-17 for 7075-T73 plate; stock certs validated within 2.3% on E via ultrasonic NDI.</t>
+          <t>Tabulated elastic and plastic material properties (E = 71.5 GPa, ν = 0.33, σ_y = 365 MPa) from MMPDS-17 for 7075-T73 plate 1.0–1.5 in, corroborated by stock cert ultrasonic NDI (within 2.3%).</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1516,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>TVAC-vibe rehearsal PSD input log (05/19/26)</t>
+          <t>TVAC-Vibe Rehearsal Log 05/19/26 — PSD Input</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Vibration PSD load averaged across two rehearsal runs, co-quantized to 1/6 octave for model boundary condition input.</t>
+          <t>Random vibration PSD (0.1 g²/Hz, 80–350 Hz) derived from TVAC-vibe rehearsal, averaged across two runs and co-quantized to 1/6 octave for model boundary condition input.</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1533,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Subcomponent 3-point bend test data — Test Lab 17</t>
+          <t>Subcomponent 3-Point Bend Test — Test Lab 17</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Physical test of geometrically similar bracket coupon (same fillet radius and thickness) with Instron 5985; two fillet strain gages and one web gage; torque-applied preload; room temperature.</t>
+          <t>Physical strain-gauge test of geometrically similar bracket coupon (same fillet radius and thickness) on Instron 5985 at room temperature, providing fillet and web strain data for FE validation comparison.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1975,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Subcomponent 3-point bend coupon correlation</t>
+          <t>Mesh Convergence Study — Critical Fillet</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1995,12 +1990,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>FE model compared against physical 3-point bend test of geometrically similar bracket coupon at Test Lab 17. Strain gages at fillet and web locations compared to FE predictions across the load range including onset of plasticity.</t>
+          <t>Three mesh refinements (1.6M / 3.2M / 6.7M DOF) at the hot fillet. Peak von Mises change: +12.1% coarse-to-medium, +3.0% medium-to-fine. Richardson extrapolation estimated asymptotic change ~2.6%. Reaction force imbalance &lt;0.5%.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Instron 5985 test data, two fillet strain gages and one web gage</t>
+          <t>Richardson-extrapolated zero-mesh-size peak stress</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2008,14 +2003,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Single deterministic comparison; friction coefficient adjusted from µ=0.25 to µ=0.22 to match test; E not tuned</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>If Yes, describe the method</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Midspan strain within 6%; fillet gage within 9% at 80% limit load; plasticity onset within 10 MPa effective stress</t>
+          <t>GCI-proxy: 3.0% medium-to-fine peak stress change; extrapolated asymptotic error ~2.6%</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2027,7 +2022,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>NAFEMS LE10 and thick-plate closed-form benchmark verification</t>
+          <t>NAFEMS LE10 and Thick-Plate Benchmark Verification</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2037,12 +2032,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>FE model with same C3D10 element family and formulation compared against NAFEMS LE10 benchmark and thick-plate-with-corner-load closed-form analytical solution to verify numerical implementation.</t>
+          <t>Abaqus model verified against NAFEMS LE10 benchmark and a thick-plate-with-corner-load closed-form solution using the same C3D10 element family and formulation. Tip deflection error 0.9–1.2%. Vendor patch tests for quadratic tets under combined bending/membrane showed no spurious modes.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>NAFEMS LE10 benchmark and closed-form analytical solution</t>
+          <t>NAFEMS LE10 reference solution and analytical thick-plate closed form</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2064,7 +2059,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Mesh convergence study at critical fillet</t>
+          <t>Subcomponent 3-Point Bend Strain Comparison</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2074,27 +2069,22 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three mesh densities (1.6M, 3.2M, 6.7M DOF) evaluated for peak von Mises stress at the hot fillet. Richardson extrapolation used to estimate asymptotic value.</t>
+          <t>FE model compared to physical coupon test (Instron 5985, Test Lab 17). Two strain gauges at the fillet and one at the web. Midspan strain within 6%; fillet gauge within 9% at 80% of limit load; onset-of-plasticity effective stress captured within 10 MPa using µ = 0.22 (vs. nominal 0.25). Elastic modulus not adjusted.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation to zero mesh size</t>
+          <t>Measured strain-gauge data from bracket coupon test</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Richardson extrapolation; estimated extrapolated peak change to zero size ≈ 2.6%</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Peak von Mises change: +12.1% coarse→medium, +3.0% medium→fine; extrapolated residual ≈ 2.6%</t>
+          <t>Midspan strain error &lt;6%; fillet strain error &lt;9%; plasticity onset error &lt;10 MPa</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2106,7 +2096,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Monte Carlo UQ — 95th/99th percentile peak von Mises</t>
+          <t>Monte Carlo UQ — Peak Fillet Stress</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2116,12 +2106,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>200-run Latin hypercube Monte Carlo varying friction coefficient, bolt preload, elastic modulus, and fillet radius machining tolerance to characterize variability in peak fillet stress and plastic strain.</t>
+          <t>200-run Latin hypercube Monte Carlo on µ ∈ [0.15, 0.35], preload ±15%, E ±3%, fillet radius ±0.15 mm. 95th-percentile peak von Mises 312 MPa; 99th-percentile 334 MPa. Plastic strain &lt;0.15% in 97% of samples. Sobol first-order indices computed via GP surrogate. Dominant driver: preload variability (index 0.47).</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Yield strength threshold (365 MPa) and plastic strain limit (0.2%)</t>
+          <t>Yield strength of 7075-T73 (365 MPa)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2131,12 +2121,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Latin hypercube Monte Carlo (200 runs); Sobol first-order indices via GP surrogate; local finite-difference sensitivity</t>
+          <t>Latin Hypercube Monte Carlo (n=200) with Gaussian Process surrogate for Sobol indices</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>95th percentile peak von Mises = 312 MPa; 99th percentile = 334 MPa; plastic strain &lt;0.15% in 97% of samples; ~50 MPa headroom to yield at 95th percentile</t>
+          <t>95th-pct σ_VM = 312 MPa (~50 MPa margin to yield); 99th-pct = 334 MPa</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2290,12 +2280,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Evidence that solver is verified, controlled, and free of known defects relevant to the analysis</t>
+          <t>Evidence of tested, versioned simulation software with known defects resolved</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023HF3 is a commercial solver with vendor-supplied QA patch tests (quadratic tets under combined bending/membrane) run and passed. The known follower-load bug (SPR 140323) present in HF1 was explicitly confirmed fixed in HF3, and bolt preload results verified stable across increments. Abaqus kernel/CAE version recorded in run logs. All scripts and .cae files stored in GitLab repo av-bracket-fea at tag v0.6.4 with conda-lock pinned Python 3.10 environment on Ubuntu 22.04 LTS. Results reproduced on a second workstation within numerical noise. Version control and reproducibility well-documented.</t>
+          <t>Abaqus/Standard 2023HF3 used with documented version in run logs. Vendor-supplied QA patch test set executed for C3D10 elements under combined bending/membrane with no spurious modes. Known follower-load bug (SPR 140323) present in HF1 confirmed fixed in HF3; preload results verified stable across increments. Conda-lock environment file pins all Python dependencies; results reproduced on a second workstation within numerical noise. GitLab repo av-bracket-fea, tag v0.6.4. Abaqus is a commercial solver with established QA processes.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2324,12 +2314,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Demonstration that the code correctly solves the governing equations for this element type and loading</t>
+          <t>Comparison to analytical or benchmark solutions demonstrates correct equation solving</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>NAFEMS LE10 benchmark and thick-plate-with-corner-load closed-form solution both compared using the same C3D10 element family and formulation; tip deflection errors of 0.9–1.2% demonstrate accurate implementation. Vendor patch tests for quadratic tets under combined bending/membrane loading showed no spurious modes. These are recognized code verification benchmarks directly applicable to the element formulation used.</t>
+          <t>NAFEMS LE10 benchmark and a thick-plate-with-corner-load closed-form solution used with the same C3D10 element family. Tip deflection errors 0.9–1.2%. Vendor patch tests for quadratic tets showed no spurious modes. These cover the element type and loading regime used in the production model.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2358,12 +2348,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Spatial discretization error at the critical fillet quantified and shown to be acceptable</t>
+          <t>Mesh convergence demonstrated with quantified error estimate at critical feature</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three mesh refinements (1.6M, 3.2M, 6.7M DOF) performed at the critical fillet. Peak von Mises changed +12.1% coarse→medium and +3.0% medium→fine. Richardson extrapolation estimated remaining error at ~2.6% relative to asymptotic value. Medium mesh selected for production runs. Reaction force imbalance &lt;0.5% for all meshes confirms global equilibrium. Temporal/incremental convergence not separately quantified but cutback events &lt;5 per step after penalty tuning.</t>
+          <t>Three systematically refined meshes (1.6M / 3.2M / 6.7M DOF) at the critical fillet. Peak von Mises changes: +12.1% (coarse→medium), +3.0% (medium→fine). Richardson extrapolation gives asymptotic change ~2.6%. Medium mesh selected for production runs. Reaction force imbalance &lt;0.5% confirming global equilibrium.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2388,16 +2378,16 @@
         <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative solver convergence demonstrated for nonlinear steps</t>
+          <t>Iterative solver and nonlinear convergence confirmed adequate</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Newton residuals dropped 4 orders of magnitude per increment in nonlinear steps, indicating tight convergence. Contact penetration averaged 3.2 µm at peak load (small relative to geometry). Cutback events &lt;5 per step after penalty tuning. No specific residual tolerance thresholds are stated explicitly in the report, but behavior described is consistent with Abaqus default tight tolerances.</t>
+          <t>Newton residuals dropped 4 orders of magnitude per increment in all nonlinear steps. Contact penetration averaged 3.2 µm at peak load. Cutback events &lt;5 per step after penalty tuning. These metrics confirm robust nonlinear convergence throughout the simulation.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2426,12 +2416,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent check or systematic review that boundary conditions, loads, and model setup are correct</t>
+          <t>Independent review or systematic checks of model setup, BCs, and post-processing</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions derived from CAD constraint map ASM-A1 and mass properties from CAD R38, providing traceable setup. Analyst holds NAFEMS PSE (Structures) certification (passed 2024) with 8 years Abaqus/Standard experience. All inputs and scripts version-controlled in GitLab. Results reproduced on a second workstation. However, no explicitly documented independent peer review or second analyst sign-off is mentioned; reproducibility check partially compensates. Limitations (omitted adhesive, simplified fastener head compliance, no thermal relaxation) are explicitly documented.</t>
+          <t>Boundary conditions derived from CAD constraint map ASM-A1 and mass properties from CAD R38. Bolt torque converted to preload using NASM1312-31 and k = 0.18. All scripts and .cae files version-controlled in GitLab (tag v0.6.4); Python environment pinned; results reproduced on a second workstation. Analyst holds NAFEMS PSE (Structures) qualification (2024) with 8 yrs Abaqus/Standard experience. However, no explicit independent peer review or separate checker sign-off is documented.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2460,12 +2450,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive model choices justified for the physics regime</t>
+          <t>Governing equations and constitutive models justified for the physics regime; limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard implicit with geometric nonlinearity enabled for contact, small-strain assumption with bilinear kinematic plasticity (yield 365 MPa, tangent 1.1 GPa) is appropriate for 7075-T73 under near-yield loading. Element choice (C3D10) justified via benchmark verification. Temperature effects explicitly excluded with justification (18–28°C enclosure). Known model limitations documented: no micro-slip wear, adhesive omitted, beam head offsets for fastener compliance, vibe linearized about preloaded state. Random vibe treatment (PSD base acceleration, linearized) is standard practice for this frequency range. Constitutive model validated against coupon test including plasticity onset.</t>
+          <t>Small-strain implicit FEA with geometric nonlinearity in contact is well-justified for quasi-static bracket loading. Bilinear kinematic plasticity for 7075-T73 is a standard choice for metallic aerospace structures. Temperature effects explicitly scoped out (18–28 °C enclosure). Known limitations documented: no micro-slip wear, adhesive under EMI gasket omitted, fastener head compliance simplified, thermal preload relaxation excluded, random vibe linearized about preloaded state. Turbulence and fluid models not applicable.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2494,12 +2484,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, loads, and boundary conditions traceable to measured or authoritative sources with uncertainty characterized</t>
+          <t>Material properties, BCs, and geometry from traceable sources with characterized uncertainty</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from MMPDS-17 (authoritative handbook for aerospace alloys); stock cert match within 2.3% on E confirmed via ultrasonic NDI. Vibe PSD from TVAC rehearsal log (05/19/26), averaged across two runs, co-quantized to 1/6 octave. Bolt torque per NASM1312-31 translated to preload with k=0.18. Input uncertainties explicitly quantified: E ±3%, preload ±15%, friction µ ∈ [0.15,0.35], fillet radius ±0.15 mm machining tolerance — all propagated through 200-run Monte Carlo. Geometry from CAD R38. High traceability and quantified uncertainty characterization.</t>
+          <t>Material properties from MMPDS-17 (7075-T73 plate 1.0–1.5 in) with stock cert ultrasonic NDI corroboration within 2.3% on E. PSD from TVAC-vibe rehearsal log 05/19/26, averaged over two runs, co-quantized to 1/6 octave. Bolt preload from NASM1312-31 with k = 0.18. Fillet radius tolerance ±0.15 mm from machining spec. Input uncertainties (E ±3%, preload ±15%, friction ±[0.15,0.35], radius ±0.15 mm) formally propagated in 200-run Monte Carlo.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2528,12 +2518,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles representative of the production bracket with adequate sample size</t>
+          <t>Test articles representative of production configuration; sample size documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>One geometrically similar bracket coupon tested (same fillet radius and thickness) at Test Lab 17. The report states "a subcomponent 3-point bend on a geometrically similar bracket coupon" without specifying the number of specimens; no statistical characterization of sample variability is provided. The coupon is described as geometrically similar but is not confirmed to be from production-representative Lot 1 material. A single coupon provides limited statistical confidence. This represents basic evidence with notable gaps in sample size and statistical characterization.</t>
+          <t>Subcomponent 3-point bend test conducted on a geometrically similar coupon (same fillet radius and thickness) at Test Lab 17 with Instron 5985. Report states two strain gauges at fillet and one at web. Number of test coupons is not explicitly stated — appears to be a single coupon test. Production representativeness is partial (similar geometry, same material assumed, but not stated to be from production lot). Sample size justification is absent.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2562,12 +2552,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions controlled and instrumented with known measurement uncertainty</t>
+          <t>Calibrated instruments, controlled environment, measured boundary conditions</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Testing performed on Instron 5985 (calibrated commercial load frame) at room temperature with preload applied via torque-to-tension per NASM1312-31. Two strain gages at fillet and one at web. Test Lab 17 is an identified facility. Temperature controlled (room temp). However, formal calibration records, gage measurement uncertainty quantification, and explicit test standard citations are not provided in the report. Conditions are reasonably well-described but formal uncertainty quantification of test measurements is absent.</t>
+          <t>Test performed on Instron 5985 (a calibrated load frame) at room temperature in Test Lab 17. Preload applied via torque-to-tension per bolt torque limits. Two fillet gauges and one web gauge used. Room temperature matches the modeled 18–28 °C operating range. Formal calibration certificates, measurement uncertainty, and test standard (ASTM/ISO) references are not explicitly cited, but use of a named, calibrated commercial load frame in a dedicated test lab is adequate evidence.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2596,12 +2586,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs matched to test conditions with documented parameter correspondence</t>
+          <t>Model inputs matched to experimental conditions with documented comparison</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Friction coefficient adjusted from nominal µ=0.25 to µ=0.22 to match test behavior (within the UQ range [0.15,0.35]); E explicitly not tuned. Bolt preload applied via torque-to-tension consistent with test procedure. Geometry matched to coupon (same fillet radius and thickness). Boundary conditions set to match 3-point bend test configuration. The adjustment of µ is documented and physically justified (single parameter, within scatter range). Formal uncertainty propagation from test measurement uncertainties to model inputs is not explicitly performed for the validation comparison.</t>
+          <t>FE model uses same fillet radius and thickness as test coupon. Friction coefficient adjusted from µ = 0.25 nominal to µ = 0.22 to match test onset-of-plasticity behavior (explicitly noted that E was not adjusted). CAD geometry, torque-to-preload conversion, and PSD boundary conditions derived from documented sources traceable to physical measurements. Monte Carlo varies inputs over physically meaningful ranges. Some gap remains in full input-to-test-condition traceability (e.g., exact coupon dimensional report not referenced).</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2630,12 +2620,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of FE predictions to test measurements at the critical locations</t>
+          <t>Quantitative comparison of model predictions to experimental data with error metrics</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative metrics reported: midspan strain within 6%, fillet gage within 9% at 80% limit load, plasticity onset captured within 10 MPa effective stress. Three gage locations compared (two fillet, one web). Comparison covers elastic and onset-of-plasticity regimes. Errors are specific and quantified. However, only a single test article is used, measurement uncertainty bands are not formally reported, and no statistical validation metric (e.g., area metric, u-pooled) is computed. Adequate for the risk level but not comprehensive.</t>
+          <t>FE vs. test: midspan strain error &lt;6%, fillet gauge error &lt;9% at 80% of limit load, onset-of-plasticity effective stress within 10 MPa. Three comparison points (midspan, fillet, web) across load range up to 80% of limit. 95th-percentile Monte Carlo peak stress (312 MPa) compared against yield (365 MPa) with 50 MPa margin. No formal statistical validation metric (e.g., u-pooled, SSRD) or uncertainty bands on test data reported; comparison is deterministic point-to-point.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2664,12 +2654,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model QoIs directly address the structural adequacy decision and can be measured both computationally and experimentally</t>
+          <t>QoIs directly address the safety/performance concern and are measurable computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Peak von Mises stress and plastic strain at the critical fillet are the primary QoIs, directly tied to the yield margin decision documented in PR-1012. These quantities are computed by the FE model and measured (via strain gages) in the physical coupon test. The 95th/99th percentile stress outputs from Monte Carlo directly map to the acceptance criterion (~50 MPa margin to yield). Sobol indices identify dominant contributors. QoIs are well-defined, decision-relevant, and both computationally and experimentally accessible.</t>
+          <t>Primary QoI is peak von Mises stress and plastic strain at the critical fillet — directly addressing the margin-to-yield safety concern flagged in PR-1012. These are measurable both computationally (element output) and experimentally (strain gauges at fillet). Secondary QoI is midspan deflection/strain for global model confidence. Sobol sensitivity indices identify preload as the dominant driver, focusing attention on the physically relevant uncertainty. QoIs are well-matched to the decision (Lot 2 release).</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2698,12 +2688,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation test conditions and geometry sufficiently representative of the actual bracket and operational loading</t>
+          <t>Validation conditions match intended use (geometry, loading, physics regime, material)</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>The 3-point bend coupon shares fillet radius and thickness with the production bracket but is a simplified subcomponent geometry under a simplified loading mode (3-point bend vs. combined quasi-static + vibe). The validation does not directly replicate the ascent load combination or the random vibe environment. The coupon test is at room temperature, consistent with the COU thermal envelope (18–28°C). No full-bracket or assembly-level test is reported. The gap between coupon validation and full COU (combined loading, actual boundary conditions, bolt pattern) is partially compensated by the UQ study but represents a meaningful limitation. Adequate but not comprehensive coverage of the COU envelope.</t>
+          <t>Subcomponent bend test used a geometrically similar coupon (same fillet radius and thickness), same material (7075-T73), same fillet geometry, and same room-temperature environment as the COU. Loading (3-point bend to 80% of limit load with bolt preload) is representative of the quasi-static component of the COU. Gaps: (1) full assembly with tray and chassis not tested; (2) random vibration loading not validated experimentally — PSD run linearized about static preloaded state with no experimental vibe comparison; (3) test was a single coupon, not a statistical sample. Despite these gaps, the validation activity is substantially relevant to the critical fillet stress QoI.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2888,7 +2878,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The FEA model of LND-AV-312 is judged adequate to support Lot 2 machining release with no design change. Mesh convergence is demonstrated with ~2.6% extrapolated residual error at the critical fillet. Code verification is supported by NAFEMS LE10 and closed-form benchmarks (errors &lt;1.2%). Subcomponent coupon validation shows FE-to-test agreement within 6–9% strain at critical locations and plasticity onset within 10 MPa. A 200-run Latin hypercube Monte Carlo characterizes uncertainty in the four dominant input parameters; the 95th percentile peak von Mises (312 MPa) retains ~50 MPa headroom to yield (365 MPa), and plastic strain remains below 0.15% in 97% of samples. Known model limitations (no micro-slip wear, omitted adhesive, linearized vibe, no thermal preload relaxation) are explicitly documented and judged acceptable for this decision. Conditions: (1) friction coefficient and preload scatter ranges should be retained in the Lot 2 acceptance test plan to bound as-built performance; (2) a second analyst independent review is recommended before Lot 3 or any design change; (3) if operating temperatures exceed 28°C or if a design change alters the fillet geometry, the analysis shall be updated.</t>
+          <t>The FEA of the LND-AV-312 avionics tray bracket is judged credible and adequate to support Lot 2 machining release with no design change. All 13 credibility factors are at or above required levels for MRL 3. Key supporting evidence: (1) mesh convergence confirmed with ~2.6% asymptotic discretization error at the critical fillet; (2) NAFEMS and analytical benchmarks verify code performance within 0.9–1.2%; (3) subcomponent 3-point bend test achieves &lt;9% strain error at the fillet; (4) 200-run Monte Carlo UQ establishes ~50 MPa margin to yield at the 95th percentile, with sub-0.2% localized plastic strain in 97% of samples; (5) all inputs are traceable to MMPDS-17, calibrated test hardware, and documented CAD/torque standards. Known limitations (no experimental vibe validation, single coupon test, linearized PSD analysis) are documented and judged acceptable given the margin retained. It is recommended that the µ and preload scatter be retained in the acceptance test plan for as-built performance bounding per analyst recommendation.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
